--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484793_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484793_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8236</v>
+        <v>2.4964</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2223</v>
+        <v>3.0275</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3988</v>
+        <v>-0.531</v>
       </c>
       <c r="G2" t="n">
         <v>4.245</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4656</v>
+        <v>0.1384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5596</v>
+        <v>0.3647</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.094</v>
+        <v>-0.2262</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0392</v>
+        <v>0.8605</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3449</v>
+        <v>0.3498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6942</v>
+        <v>0.5107</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0095</v>
+        <v>0.6344</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8515</v>
+        <v>-1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.158</v>
+        <v>2.3444</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4839</v>
+        <v>1.1772</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6073</v>
+        <v>-0.929</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1234</v>
+        <v>2.1062</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5256</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2442</v>
+        <v>-0.781</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2814</v>
+        <v>0.2383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1051</v>
+        <v>-0.4532</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8288</v>
+        <v>-0.1858</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2763</v>
+        <v>-0.2674</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3591</v>
+        <v>0.507</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0987</v>
+        <v>-0.1608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4578</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6344</v>
+        <v>-1.0095</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.71</v>
+        <v>-0.8515</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3444</v>
+        <v>-0.158</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1772</v>
+        <v>-0.4839</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.929</v>
+        <v>-0.6073</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1062</v>
+        <v>0.1234</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5256</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.781</v>
+        <v>-0.2442</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2383</v>
+        <v>-0.2814</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9547</v>
+        <v>0.573</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6343</v>
+        <v>0.3231</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3204</v>
+        <v>0.2498</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.097</v>
+        <v>0.2171</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3985</v>
+        <v>-0.4371</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4955</v>
+        <v>0.6542</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0458</v>
@@ -922,13 +922,13 @@
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1428</v>
+        <v>0.2629</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6261</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.522</v>
+        <v>-0.3632</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3959</v>
+        <v>-1.054</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.0149</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9367</v>
+        <v>-1.0689</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6466</v>
@@ -1000,13 +1000,13 @@
         <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2697</v>
+        <v>0.6116</v>
       </c>
       <c r="T7" t="n">
-        <v>0.974</v>
+        <v>0.4482</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2958</v>
+        <v>0.1635</v>
       </c>
       <c r="V7" t="n">
         <v>0.6036</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0096</v>
+        <v>-2.505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.928</v>
+        <v>-1.9466</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9375</v>
+        <v>-0.5584</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3081</v>
+        <v>-1.1329</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7443</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0523</v>
+        <v>-0.1515</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8701</v>
+        <v>-0.6073</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7538</v>
+        <v>-0.6073</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1163</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1782</v>
+        <v>-0.5256</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0095</v>
+        <v>-0.3741</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1687</v>
+        <v>-0.1515</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2228</v>
+        <v>0.628</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1118</v>
+        <v>0.2459</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3346</v>
+        <v>0.3821</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4904</v>
+        <v>-0.3018</v>
       </c>
       <c r="W8" t="n">
         <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7922</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6386</v>
+        <v>-2.5572</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2389</v>
+        <v>0.9095</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3996</v>
+        <v>-3.4666</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1329</v>
+        <v>-0.3081</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.7443</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1515</v>
+        <v>-1.0523</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6073</v>
+        <v>1.8701</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6073</v>
+        <v>1.7538</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1163</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5256</v>
+        <v>-2.1782</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3741</v>
+        <v>-1.0095</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1515</v>
+        <v>-1.1687</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4944</v>
+        <v>-0.3248</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0465</v>
+        <v>-0.1303</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5407999999999999</v>
+        <v>-0.1945</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>-2.4904</v>
       </c>
       <c r="W9" t="n">
         <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9522</v>
+        <v>-2.7289</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8769</v>
+        <v>-1.7593</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0753</v>
+        <v>-0.9695</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0916</v>
@@ -1234,13 +1234,13 @@
         <v>0.7548</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.4485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3527</v>
+        <v>-0.2352</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3192</v>
+        <v>-0.2134</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7369</v>
+        <v>-3.6644</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9188</v>
+        <v>-1.2166</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8182</v>
+        <v>-2.4478</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0331</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5342</v>
+        <v>-1.4617</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2222</v>
+        <v>-0.52</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.312</v>
+        <v>-0.9417</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9244</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0254</v>
+        <v>-6.3349</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0109</v>
+        <v>-2.4263</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0144</v>
+        <v>-3.9086</v>
       </c>
       <c r="G12" t="n">
         <v>-3.368</v>
@@ -1390,13 +1390,13 @@
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9782</v>
+        <v>-0.2878</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7519</v>
+        <v>-0.1673</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2263</v>
+        <v>-0.1205</v>
       </c>
       <c r="V12" t="n">
         <v>-1.547</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.0832</v>
+        <v>-7.8778</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3285</v>
+        <v>-3.3083</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.7547</v>
+        <v>-4.5695</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3963</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9129</v>
+        <v>-0.7076</v>
       </c>
       <c r="T13" t="n">
-        <v>0.074</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.987</v>
+        <v>-0.8018</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9434</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.9059</v>
+        <v>-22.0242</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.218200000000001</v>
+        <v>-6.3363</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.6877</v>
+        <v>-15.6876</v>
       </c>
       <c r="G14" t="n">
         <v>-10.5355</v>
@@ -1546,13 +1546,13 @@
         <v>12.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3515</v>
+        <v>-1.4697</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01820000000000051</v>
+        <v>0.8635999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.3334</v>
+        <v>-2.3333</v>
       </c>
       <c r="V14" t="n">
         <v>-6.244999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.4047</v>
+        <v>10.9954</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0712</v>
+        <v>6.5583</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3336</v>
+        <v>4.437</v>
       </c>
       <c r="G15" t="n">
         <v>6.5996</v>
@@ -1624,13 +1624,13 @@
         <v>3.2079</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3268</v>
+        <v>0.2638</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3963</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="V15" t="n">
         <v>3.7546</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.477499999999999</v>
+        <v>8.186</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3564</v>
+        <v>6.8406</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1211</v>
+        <v>1.3454</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4895</v>
+        <v>6.839</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2468</v>
+        <v>5.8734</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7574</v>
+        <v>0.9656</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4307</v>
+        <v>6.0875</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2576</v>
+        <v>4.7543</v>
       </c>
       <c r="L16" t="n">
-        <v>0.173</v>
+        <v>1.3332</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0588</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9892</v>
+        <v>1.1191</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9304</v>
+        <v>-0.3676</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9505</v>
+        <v>-0.9928</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7752</v>
+        <v>-0.4921</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1753</v>
+        <v>-0.5008</v>
       </c>
       <c r="V16" t="n">
-        <v>3.094</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>3.094</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.1132</v>
+        <v>6.7684</v>
       </c>
       <c r="E17" t="n">
-        <v>6.4508</v>
+        <v>4.2846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6623</v>
+        <v>2.4838</v>
       </c>
       <c r="G17" t="n">
-        <v>6.839</v>
+        <v>1.4895</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8734</v>
+        <v>2.2468</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9656</v>
+        <v>-0.7574</v>
       </c>
       <c r="J17" t="n">
-        <v>6.0875</v>
+        <v>1.4307</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7543</v>
+        <v>1.2576</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3332</v>
+        <v>0.173</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1191</v>
+        <v>0.9892</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3676</v>
+        <v>-0.9304</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0657</v>
+        <v>1.2414</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8818</v>
+        <v>0.7034</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1839</v>
+        <v>0.538</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6415999999999999</v>
+        <v>3.094</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2452</v>
+        <v>3.094</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3909</v>
+        <v>3.1649</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6054</v>
+        <v>2.643</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7855</v>
+        <v>0.5219</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8551</v>
+        <v>2.5011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1604</v>
+        <v>3.4732</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6947</v>
+        <v>-0.9721</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1709</v>
+        <v>4.1743</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1042</v>
+        <v>2.8737</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0667</v>
+        <v>1.3006</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3158</v>
+        <v>-1.6732</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9438</v>
+        <v>0.5995</v>
       </c>
       <c r="O18" t="n">
-        <v>0.628</v>
+        <v>-2.2727</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7548</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4832</v>
+        <v>0.5507</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1328</v>
+        <v>0.0539</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.616</v>
+        <v>0.4968</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2642</v>
+        <v>0.3018</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X18" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8935</v>
+        <v>2.724</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7661</v>
+        <v>1.7029</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1275</v>
+        <v>1.0212</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5011</v>
+        <v>0.8551</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4732</v>
+        <v>0.1604</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9721</v>
+        <v>0.6947</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1743</v>
+        <v>1.1709</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8737</v>
+        <v>1.1042</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3006</v>
+        <v>0.0667</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6732</v>
+        <v>-0.3158</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5995</v>
+        <v>-0.9438</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2727</v>
+        <v>0.628</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7207</v>
+        <v>-0.1501</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.823</v>
+        <v>0.2302</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1023</v>
+        <v>-0.3803</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3018</v>
+        <v>1.2642</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8185</v>
+        <v>0.0307</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2194</v>
+        <v>-2.9015</v>
       </c>
       <c r="F20" t="n">
-        <v>3.038</v>
+        <v>2.9321</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9101</v>
@@ -2014,13 +2014,13 @@
         <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6154</v>
+        <v>0.8276</v>
       </c>
       <c r="T20" t="n">
-        <v>1.138</v>
+        <v>0.456</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4774</v>
+        <v>0.3716</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6415999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-1.5795</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5621</v>
+        <v>-0.4122</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1937</v>
+        <v>-1.1673</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6103</v>
@@ -2092,13 +2092,13 @@
         <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9787</v>
+        <v>1.0308</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6671</v>
+        <v>0.6927</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3116</v>
+        <v>0.338</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2752</v>
+        <v>-2.325</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5829</v>
+        <v>0.0017</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6923</v>
+        <v>-2.3267</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5222</v>
@@ -2170,13 +2170,13 @@
         <v>0.5661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6966</v>
+        <v>0.2537</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4703</v>
+        <v>0.1143</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2263</v>
+        <v>0.1394</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2855</v>
+        <v>-3.7598</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.322</v>
+        <v>-3.0297</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9635</v>
+        <v>-0.7301</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7062</v>
@@ -2248,13 +2248,13 @@
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0999</v>
+        <v>0.6256</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1916</v>
+        <v>0.4839</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0917</v>
+        <v>0.1417</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>22.906</v>
+        <v>24.2051</v>
       </c>
       <c r="E24" t="n">
         <v>15.6877</v>
       </c>
       <c r="F24" t="n">
-        <v>7.218499999999999</v>
+        <v>8.517300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>10.5355</v>
@@ -2296,7 +2296,7 @@
         <v>10.6433</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1079000000000003</v>
+        <v>-0.1078999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>16.9606</v>
@@ -2305,7 +2305,7 @@
         <v>10.9014</v>
       </c>
       <c r="L24" t="n">
-        <v>6.058999999999999</v>
+        <v>6.059000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-6.425</v>
@@ -2314,7 +2314,7 @@
         <v>-0.2582000000000002</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.1667</v>
+        <v>-6.166700000000001</v>
       </c>
       <c r="P24" t="n">
         <v>3.774</v>
@@ -2326,22 +2326,22 @@
         <v>16.0395</v>
       </c>
       <c r="S24" t="n">
-        <v>2.351499999999999</v>
+        <v>3.6507</v>
       </c>
       <c r="T24" t="n">
-        <v>2.333299999999999</v>
+        <v>2.3332</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0182000000000001</v>
+        <v>1.3173</v>
       </c>
       <c r="V24" t="n">
-        <v>6.244999999999998</v>
+        <v>6.244999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>8.6594</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4144</v>
+        <v>-2.414400000000001</v>
       </c>
     </row>
   </sheetData>
